--- a/artfynd/A 23182-2025 artfynd.xlsx
+++ b/artfynd/A 23182-2025 artfynd.xlsx
@@ -954,12 +954,7 @@
         <v>74770898</v>
       </c>
       <c r="B4" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -991,10 +986,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563317.2284241536</v>
+        <v>563317</v>
       </c>
       <c r="R4" t="n">
-        <v>6261928.845845293</v>
+        <v>6261929</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1024,19 +1019,9 @@
           <t>1990-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 23182-2025 artfynd.xlsx
+++ b/artfynd/A 23182-2025 artfynd.xlsx
@@ -954,7 +954,7 @@
         <v>74770898</v>
       </c>
       <c r="B4" t="n">
-        <v>98622</v>
+        <v>98625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23182-2025 artfynd.xlsx
+++ b/artfynd/A 23182-2025 artfynd.xlsx
@@ -954,7 +954,7 @@
         <v>74770898</v>
       </c>
       <c r="B4" t="n">
-        <v>98625</v>
+        <v>98626</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23182-2025 artfynd.xlsx
+++ b/artfynd/A 23182-2025 artfynd.xlsx
@@ -954,7 +954,7 @@
         <v>74770898</v>
       </c>
       <c r="B4" t="n">
-        <v>98626</v>
+        <v>98653</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23182-2025 artfynd.xlsx
+++ b/artfynd/A 23182-2025 artfynd.xlsx
@@ -954,7 +954,7 @@
         <v>74770898</v>
       </c>
       <c r="B4" t="n">
-        <v>98653</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23182-2025 artfynd.xlsx
+++ b/artfynd/A 23182-2025 artfynd.xlsx
@@ -954,7 +954,7 @@
         <v>74770898</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23182-2025 artfynd.xlsx
+++ b/artfynd/A 23182-2025 artfynd.xlsx
@@ -954,7 +954,7 @@
         <v>74770898</v>
       </c>
       <c r="B4" t="n">
-        <v>98666</v>
+        <v>98670</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23182-2025 artfynd.xlsx
+++ b/artfynd/A 23182-2025 artfynd.xlsx
@@ -954,7 +954,7 @@
         <v>74770898</v>
       </c>
       <c r="B4" t="n">
-        <v>98670</v>
+        <v>98677</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23182-2025 artfynd.xlsx
+++ b/artfynd/A 23182-2025 artfynd.xlsx
@@ -954,7 +954,7 @@
         <v>74770898</v>
       </c>
       <c r="B4" t="n">
-        <v>98680</v>
+        <v>98685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23182-2025 artfynd.xlsx
+++ b/artfynd/A 23182-2025 artfynd.xlsx
@@ -954,7 +954,7 @@
         <v>74770898</v>
       </c>
       <c r="B4" t="n">
-        <v>98685</v>
+        <v>98693</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23182-2025 artfynd.xlsx
+++ b/artfynd/A 23182-2025 artfynd.xlsx
@@ -954,7 +954,7 @@
         <v>74770898</v>
       </c>
       <c r="B4" t="n">
-        <v>98693</v>
+        <v>98703</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23182-2025 artfynd.xlsx
+++ b/artfynd/A 23182-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,74 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60357532</v>
+        <v>74770898</v>
       </c>
       <c r="B2" t="n">
-        <v>44335</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102021</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Yggesbo, Sm</t>
+          <t>Yggesbo västra gdn 300 m V, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>563471.9164846301</v>
+        <v>563317</v>
       </c>
       <c r="R2" t="n">
-        <v>6261867.684217287</v>
+        <v>6261929</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -766,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-06-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1990-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-06-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1990-12-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Smålands flora 2007: KOO: 4G2c 3337. SOM: Platanthera bifolia. LEG: Thomas Karlsson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,268 +762,23 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Bakom lada i fd ängsmark</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marcus Vestlund</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marcus Vestlund</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>62174957</v>
-      </c>
-      <c r="B3" t="n">
-        <v>5104</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>100276</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Prydnadsbock</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Anaglyptus mysticus</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>fälla</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Halltorp Behandling, solbelyst, Sm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>563471.9164846301</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6261867.684217287</v>
-      </c>
-      <c r="S3" t="n">
-        <v>50</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Halltorp</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2016-05-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2016-06-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>I feromonfälla för långhorning</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>Marcus Vestlund</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Marcus Vestlund</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Marcus Vestlund, Mikael Molander</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Phero Bio SLU</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>74770898</v>
-      </c>
-      <c r="B4" t="n">
-        <v>98703</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>219874</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Nattviol</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Platanthera bifolia</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Yggesbo västra gdn 300 m V, Sm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>563317</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6261929</v>
-      </c>
-      <c r="S4" t="n">
-        <v>50</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Halltorp</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>1990-01-01</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 4G2c 3337. SOM: Platanthera bifolia. LEG: Thomas Karlsson</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Bakom lada i fd ängsmark</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
           <t>Via Margareta Edqvist</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY2" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
         </is>

--- a/artfynd/A 23182-2025 artfynd.xlsx
+++ b/artfynd/A 23182-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,8 +788,16 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74770898</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>